--- a/crates/xlstream-eval/tests/fixtures/math/logarithms.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/math/logarithms.xlsx
@@ -22,19 +22,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">val</t>
   </si>
   <si>
     <t xml:space="preserve">ln</t>
   </si>
   <si>
-    <t xml:space="preserve">log</t>
+    <t xml:space="preserve">log10_fn</t>
   </si>
   <si>
-    <t xml:space="preserve">exp</t>
+    <t xml:space="preserve">log_base10</t>
   </si>
   <si>
-    <t xml:space="preserve">log10</t>
+    <t xml:space="preserve">exp_fn</t>
   </si>
 </sst>
 </file>
@@ -110,12 +110,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -314,231 +310,231 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">LN(ABS(A2)+1)</f>
-        <v>2.39789527279837</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <f aca="false">LOG(ABS(A2)+1,10)</f>
-        <v>1.04139268515823</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B2" s="0" t="n">
+        <f aca="false">LN(A2)</f>
+        <v>2.30258509299405</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false">LOG10(A2)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <f aca="false">LOG(A2,10)</f>
+        <v>1</v>
       </c>
       <c r="E2" s="0" t="n">
-        <f aca="false">LOG10(ABS(A2)+1)</f>
-        <v>1.04139268515823</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <f aca="false">LN(ABS(A3)+1)</f>
-        <v>3.25809653802148</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <f aca="false">LOG(ABS(A3)+1,10)</f>
-        <v>1.41497334797082</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B3" s="0" t="n">
+        <f aca="false">LN(A3)</f>
+        <v>3.2188758248682</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false">LOG10(A3)</f>
+        <v>1.39794000867204</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <f aca="false">LOG(A3,10)</f>
+        <v>1.39794000867204</v>
       </c>
       <c r="E3" s="0" t="n">
-        <f aca="false">LOG10(ABS(A3)+1)</f>
-        <v>1.41497334797082</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <f aca="false">LN(A4)</f>
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <f aca="false">LN(ABS(A4)+1)</f>
+      <c r="C4" s="0" t="n">
+        <f aca="false">LOG10(A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <f aca="false">LOG(ABS(A4)+1,10)</f>
+      <c r="D4" s="0" t="n">
+        <f aca="false">LOG(A4,10)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
-      </c>
       <c r="E4" s="0" t="n">
-        <f aca="false">LOG10(ABS(A4)+1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <f aca="false">LN(ABS(A5)+1)</f>
-        <v>4.61512051684126</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <f aca="false">LOG(ABS(A5)+1,10)</f>
-        <v>2.00432137378264</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B5" s="0" t="n">
+        <f aca="false">LN(A5)</f>
+        <v>4.60517018598809</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false">LOG10(A5)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <f aca="false">LOG(A5,10)</f>
+        <v>2</v>
       </c>
       <c r="E5" s="0" t="n">
-        <f aca="false">LOG10(ABS(A5)+1)</f>
-        <v>2.00432137378264</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>-5</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <f aca="false">LN(ABS(A6)+1)</f>
-        <v>1.79175946922806</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <f aca="false">LOG(ABS(A6)+1,10)</f>
-        <v>0.778151250383644</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <f aca="false">LN(A6)</f>
+        <v>-0.693147180559945</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false">LOG10(A6)</f>
+        <v>-0.301029995663981</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <f aca="false">LOG(A6,10)</f>
+        <v>-0.301029995663981</v>
       </c>
       <c r="E6" s="0" t="n">
-        <f aca="false">LOG10(ABS(A6)+1)</f>
-        <v>0.778151250383644</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <f aca="false">LN(ABS(A7)+1)</f>
-        <v>3.93182563272433</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <f aca="false">LOG(ABS(A7)+1,10)</f>
-        <v>1.70757017609794</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B7" s="0" t="n">
+        <f aca="false">LN(A7)</f>
+        <v>3.91202300542815</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false">LOG10(A7)</f>
+        <v>1.69897000433602</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <f aca="false">LOG(A7,10)</f>
+        <v>1.69897000433602</v>
       </c>
       <c r="E7" s="0" t="n">
-        <f aca="false">LOG10(ABS(A7)+1)</f>
-        <v>1.70757017609794</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <f aca="false">LN(ABS(A8)+1)</f>
-        <v>4.33073334028633</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <f aca="false">LOG(ABS(A8)+1,10)</f>
-        <v>1.88081359228079</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B8" s="0" t="n">
+        <f aca="false">LN(A8)</f>
+        <v>4.31748811353631</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <f aca="false">LOG10(A8)</f>
+        <v>1.8750612633917</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <f aca="false">LOG(A8,10)</f>
+        <v>1.8750612633917</v>
       </c>
       <c r="E8" s="0" t="n">
-        <f aca="false">LOG10(ABS(A8)+1)</f>
-        <v>1.88081359228079</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <f aca="false">LN(ABS(A9)+1)</f>
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <f aca="false">LN(A9)</f>
         <v>0.693147180559945</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <f aca="false">LOG(ABS(A9)+1,10)</f>
+      <c r="C9" s="0" t="n">
+        <f aca="false">LOG10(A9)</f>
         <v>0.301029995663981</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="D9" s="0" t="n">
+        <f aca="false">LOG(A9,10)</f>
+        <v>0.301029995663981</v>
       </c>
       <c r="E9" s="0" t="n">
-        <f aca="false">LOG10(ABS(A9)+1)</f>
-        <v>0.301029995663981</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="B10" s="1" t="n">
-        <f aca="false">LN(ABS(A10)+1)</f>
-        <v>6.90775527898214</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <f aca="false">LOG(ABS(A10)+1,10)</f>
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B10" s="0" t="n">
+        <f aca="false">LN(A10)</f>
+        <v>6.90675477864855</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <f aca="false">LOG10(A10)</f>
+        <v>2.99956548822598</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <f aca="false">LOG(A10,10)</f>
+        <v>2.99956548822598</v>
       </c>
       <c r="E10" s="0" t="n">
-        <f aca="false">LOG10(ABS(A10)+1)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="B11" s="1" t="n">
-        <f aca="false">LN(ABS(A11)+1)</f>
-        <v>3.76120011569356</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <f aca="false">LOG(ABS(A11)+1,10)</f>
-        <v>1.63346845557959</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+      <c r="B11" s="0" t="n">
+        <f aca="false">LN(A11)</f>
+        <v>3.73766961828337</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <f aca="false">LOG10(A11)</f>
+        <v>1.6232492903979</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <f aca="false">LOG(A11,10)</f>
+        <v>1.6232492903979</v>
       </c>
       <c r="E11" s="0" t="n">
-        <f aca="false">LOG10(ABS(A11)+1)</f>
-        <v>1.63346845557959</v>
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
       </c>
     </row>
   </sheetData>
